--- a/Employee_Reports_wi48/Mohamed Ahthir Abdul Majeed Q0570.xlsx
+++ b/Employee_Reports_wi48/Mohamed Ahthir Abdul Majeed Q0570.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-59</v>
+        <v>-62</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-61</v>
+        <v>-64</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
